--- a/src/DEL/ex03_DEL_streams.xlsx
+++ b/src/DEL/ex03_DEL_streams.xlsx
@@ -365,7 +365,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -385,11 +385,6 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -405,18 +400,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1087,106 +1079,106 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="F21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="2" t="s">
         <v>115</v>
       </c>
     </row>
